--- a/medford_otsasyvateli_khirurgicheskie.xlsx
+++ b/medford_otsasyvateli_khirurgicheskie.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Отсасыватели хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS — всего 20 позиций.</t>
+          <t>Отсасыватели хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_otsasyvateli_khirurgicheskie.xlsx
+++ b/medford_otsasyvateli_khirurgicheskie.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать отсасыватели хирургические для клиники?</t>
+          <t>Что такое хирургический аспиратор?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Тип ? Предлагаем указанную область применения, но вы можете использовать товар по вашему усмотрению, Диапазон отрицательного давления, кПа, Потребляемая мощность, ВА, Объем емкости для сбора, мл). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Хирургический аспиратор (отсасыватель) — устройство, создающее вакуум для удаления из ран, полостей тела и дыхательных путей крови, гноя, слизи, промывочных жидкостей и мелких фрагментов тканей. Он обеспечивает хирургу обзор операционного поля, снижает риск инфицирования и повышает точность манипуляций.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем переносной аспиратор отличается от передвижного?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Переносные модели компактны, часто с аккумулятором, подходят для скорой помощи, палат и амбулаторных задач. Передвижные аппараты на стойке мощнее, несут больший резервуар и рассчитаны на постоянную установку в операционной или процедурном кабинете. Выбор зависит от места и интенсивности работы.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какой уровень вакуума нужен?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены ATMOS. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Уровень отрицательного давления измеряют в кПа. Для санации дыхательных путей и деликатных задач подходит регулируемый умеренный вакуум, для операционной — высокие значения. В каталоге диапазон от 18–73 кПа у Medela Clario до 98 кПа у ATMOS Record 55. Регулировка позволяет настроить вакуум под ситуацию.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какой объём резервуара выбрать?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Для санации и амбулаторных процедур достаточно 1000 мл. Для длительных и объёмных операций выбирают модели на 3000–5000 мл или с двумя ёмкостями, чтобы не прерывать работу при заполнении банки. Объём подбирают под характер вмешательств и ожидаемый объём эвакуируемой жидкости.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Как называется аппарат для санации дыхательных путей?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Для санации дыхательных путей применяют медицинский отсасыватель (аспиратор). В интенсивной терапии и реанимации он удаляет секрет из дыхательных путей и лёгких, в неонатологии — очищает дыхательные пути новорождённых. Для этих задач подбирают модель с регулируемым щадящим вакуумом.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что такое хирургический аспиратор?</t>
+          <t>Есть ли аспираторы для детей?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Да, выпускают педиатрические модели с настройкой на щадящий вакуум — например, Армед 7Е-В5 с диапазоном давления около 75 кПа и ёмкостью 1000 мл. Параметры для конкретного пациента и допустимый уровень разрежения определяет врач исходя из клинической ситуации.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какой аппарат высасывает мокроту?</t>
+          <t>Зачем нужен антибактериальный фильтр и клапан защиты?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Клапан защиты от переполнения не даёт жидкости попасть в насос при заполнении банки, а антибактериальный фильтр задерживает бактерии на пути к помпе. Вместе они защищают аппарат от повреждения и снижают риск перекрёстного загрязнения между процедурами.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение Росздравнадзора?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Да. Хирургический отсасыватель — медицинское изделие, и его применение в клинике в РФ требует действующего регистрационного удостоверения Росздравнадзора. Перед закупкой запросите документ на конкретную модель у поставщика и убедитесь в его актуальности.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>otsasyvateli_khirurgicheskie</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Отсасыватели хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS.</t>
+          <t>Отсасыватели хирургические (аспираторы) — медицинские устройства, создающие вакуум для удаления из ран, полостей тела и дыхательных путей крови, гноя, слизи и промывочных жидкостей. В каталоге представлены переносные и передвижные модели Fazzini, Armed (Армед), ATMOS, Medela и ФОТЕК с диапазоном отрицательного давления от 18 до 98 кПа. Объём ёмкости для сбора варьирует от 500 до 5000 мл, потребляемая мощность — от 47 до 270 ВА. Отдельно представлены педиатрические аппараты и аспираторы-ирригаторы.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Отсасыватели в каталоге: характеристики по моделям</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое отсасыватели хирургические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4568,21 +4606,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Отсасыватели в каталоге: характеристики по моделям</t>
         </is>
       </c>
     </row>
@@ -4594,201 +4631,271 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Исполнение</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Тип ? Предлагаем указанную область применения, но вы можете использовать товар по вашему усмотрению</t>
+          <t>Вакуум, кПа</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Диапазон отрицательного давления, кПа</t>
+          <t>Ёмкость, мл</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Потребляемая мощность, ВА</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Объем емкости для сбора, мл</t>
+          <t>Мощность, ВА</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Аспиратор для хирургии CHS-708</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Fazzini F-30</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Переносной</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Передвижной</t>
+          <t>до 80</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>3000</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Медицинский отсасыватель Fazzini F-30</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>Fazzini F-90</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Передвижной</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Переносной</t>
+          <t>до 80</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>до 80</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1000</t>
+          <t>240</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Педиатрический отсасыватель Армед 7Е-В5</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>Fazzini F-100 (липосакция)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Передвижной</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Переносной</t>
+          <t>до 80</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1000</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Отсасыватель медицинский Армед 7A-23B-1</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+          <t>Армед 7A-23B</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Передвижной</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Передвижной</t>
+          <t>20-90</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>20-90</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>180</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>2500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Передвижной медицинский отсасыватель Fazzini F-60</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
+          <t>Армед 7Е-В5 (педиатрический)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Переносной</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Передвижной</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>до 80</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Медицинский отсос FAZZINI F-40</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
+          <t>ATMOS C 451</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Передвижной</t>
+        </is>
+      </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1500/3000/5000</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ATMOS Record 55</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Передвижной</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>3000/5000</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Medela Clario</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>Переносной</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>до 80</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>18-73</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Medela Dominant Flex</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Передвижной</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>до 95</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1500-2500</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>120</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1000</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4800,7 +4907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5126,12 +5233,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите область применения</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается отсасыватели хирургические: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Санация дыхательных путей, малая хирургия, операционная, липосакция и педиатрия предъявляют разные требования. Для реанимации важна санация секрета, для операционной — производительность и объём. Педиатрические модели (Армед 7Е-В5) настроены на щадящий вакуум. Задача определяет класс аппарата.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5171,12 +5278,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите уровень вакуума</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Уровень отрицательного давления измеряется в кПа: в каталоге от 18–73 кПа (Medela Clario) до 98 кПа (ATMOS Record 55, CHS-708). Чем выше значение, тем эффективнее эвакуация густых сред. Для деликатных задач нужен регулируемый диапазон, для операционной — высокий вакуум с запасом.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5216,12 +5323,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Подберите объём резервуара</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Тип ? Предлагаем указанную область применения, но вы можете использовать товар по вашему усмотрению, Диапазон отрицательного давления, кПа, Потребляемая мощность, ВА, Объем емкости для сбора, мл. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Ёмкость для сбора варьирует от 500 мл (Medela Clario) до 5000 мл (ATMOS). Для длительных операций удобны модели с двумя ёмкостями или большим объёмом, чтобы не прерывать процесс при заполнении. Для санации и амбулаторных задач достаточно 1000 мл.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5261,12 +5368,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Определитесь с мобильностью</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: ATMOS.</t>
+          <t>Переносные аппараты (Fazzini F-30, Армед 7E-D) компактны и подходят для скорой помощи и палат. Передвижные на стойке (ATMOS C 451, Fazzini F-90) мощнее и рассчитаны на постоянную установку в операционной. Модели с комбинированным питанием (Fazzini F-31) работают автономно.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5306,12 +5413,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Оцените фильтрацию и защиту</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Клапан защиты от переполнения и антибактериальный фильтр предотвращают попадание жидкости и бактерий в насос. Это продлевает ресурс помпы и защищает от перекрёстного загрязнения. Наличие ножной педали освобождает руки хирурга при работе в стерильной зоне.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5351,12 +5458,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Учтите шум и обработку</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>В операционных и реанимации предпочтительны тихие мембранные аппараты. Части, контактирующие с пациентом, должны легко разбираться и стерилизоваться, в том числе в автоклаве (автоклавируемые банки). Проверьте наличие регистрационного удостоверения Росздравнадзора на выбранную модель.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5406,7 +5513,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Отсасыватели хирургические подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены ATMOS. При выборе обращают внимание на тип ? предлагаем указанную область применения, диапазон отрицательного давления, потребляемая мощность, объем емкости для сбора, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Аспиратор подбирают под задачу: для санации дыхательных путей и малых манипуляций хватает переносной модели с умеренным вакуумом, для операционной нужен передвижной аппарат с большим резервуаром и запасом производительности. Смотрю на уровень отрицательного давления в кПа, объём банки и возможность работы с двумя ёмкостями без остановки. Для реанимации и операционных отдельно оцениваю уровень шума и то, насколько легко части разбираются под стерилизацию.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5690,13 +5797,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое отсасыватели хирургические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Отсасыватели хирургические — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов ATMOS. Подберём вариант под задачи вашего отделения.</t>
+          <t>Хирургический отсасыватель создаёт вакуум и удаляет из операционного поля, полостей и дыхательных путей кровь, слизь, гной и промывочные жидкости, обеспечивая обзор и снижая риск инфицирования. Основные параметры выбора — уровень вакуума (в каталоге 18–98 кПа), объём резервуара (500–5000 мл), мобильность и уровень шума. По исполнению аппараты делят на переносные и передвижные, по назначению — от санации дыхательных путей до липосакции. В каталоге модели Fazzini, Армед, ATMOS, Medela и ФОТЕК, включая педиатрические.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5733,13 +5840,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Как устроен хирургический отсасыватель</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Тип ? Предлагаем указанную область применения, но вы можете использовать товар по вашему усмотрению, Диапазон отрицательного давления, кПа, Потребляемая мощность, ВА, Объем емкости для сбора, мл), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Основные компоненты аспиратора: компрессор или помпа, создающая вакуум (поршневые мощнее, мембранные тише и точнее в настройке); система шлангов и насадок, соединяющая насос с наконечником; резервуар для сбора жидкости с градуировкой; система защиты из клапанов и фильтров, предотвращающая переполнение и попадание бактерий в насос. От типа помпы зависят производительность и уровень шума аппарата.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5776,13 +5883,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Виды аспираторов</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>По типу использования отсасыватели делят на портативные (переносные) — компактные модели, часто с аккумулятором, для скорой помощи и палат, и стационарные (передвижные) — мощные аппараты для операционных и процедурных. По типу питания различают ручные (механические), не требующие электричества для малых объёмов, и электрические (автоматические) с большей мощностью и дополнительными функциями.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5819,13 +5926,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Параметры выбора</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>При подборе учитывают мощность и производительность, уровень вакуума в кПа, объём резервуара (для длительных операций удобны две ёмкости), дополнительные функции — антибактериальный фильтр, клапан защиты от переполнения, ножную педаль. Для портативных моделей важна автономность, для операционных и реанимации — низкий уровень шума и разборность частей под стерилизацию.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5842,6 +5949,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Области применения</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Помимо хирургии, отсасыватели применяют в акушерстве и гинекологии, стоматологии (удаление слюны и осколков), интенсивной терапии и реанимации (санация дыхательных путей), неонатологии (очистка дыхательных путей новорождённых) и эндоскопии. Отдельные модели рассчитаны на специфические задачи — например, хирургический отсос Fazzini F-100 для липосакции с ёмкостью 4000 мл.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>otsasyvateli_khirurgicheskie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
